--- a/xlsx/Power/pgroups4.xlsx
+++ b/xlsx/Power/pgroups4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F72C648-7C87-4DF7-8D65-92CBF5812184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161D9D25-D37D-4E97-A85E-B29A10E7F5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1630A4E4-CC0E-43EA-BDFD-FFFD95EF5ED6}"/>
+    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1630A4E4-CC0E-43EA-BDFD-FFFD95EF5ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="C1">
-        <v>2.5999999999999999E-2</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D1">
-        <v>0.19900000000000001</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="E1">
-        <v>0.33800000000000002</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="F1">
-        <v>0.495</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="G1">
-        <v>0.623</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="H1">
-        <v>0.71699999999999997</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="I1">
-        <v>0.76200000000000001</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="J1">
-        <v>0.80900000000000005</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="C2">
-        <v>4.0000000000000001E-3</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="D2">
-        <v>0.128</v>
+        <v>0.43</v>
       </c>
       <c r="E2">
-        <v>0.26500000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="F2">
-        <v>0.39600000000000002</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="G2">
-        <v>0.495</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="H2">
-        <v>0.61699999999999999</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="I2">
-        <v>0.67300000000000004</v>
+        <v>0.77</v>
       </c>
       <c r="J2">
-        <v>0.72799999999999998</v>
+        <v>0.80800000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.247</v>
       </c>
       <c r="C3">
-        <v>0.40300000000000002</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="D3">
-        <v>0.50700000000000001</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="E3">
-        <v>0.56999999999999995</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="F3">
-        <v>0.64</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="G3">
         <v>0.7</v>
       </c>
       <c r="H3">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="I3">
         <v>0.77</v>
       </c>
-      <c r="I3">
-        <v>0.77100000000000002</v>
-      </c>
       <c r="J3">
-        <v>0.80500000000000005</v>
+        <v>0.80300000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14299999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="B4">
-        <v>0.221</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="C4">
-        <v>0.311</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="D4">
-        <v>0.40899999999999997</v>
+        <v>0.41</v>
       </c>
       <c r="E4">
-        <v>0.48699999999999999</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="F4">
-        <v>0.56200000000000006</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="G4">
         <v>0.61799999999999999</v>
       </c>
       <c r="H4">
-        <v>0.68700000000000006</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="I4">
         <v>0.69399999999999995</v>
       </c>
       <c r="J4">
-        <v>0.746</v>
+        <v>0.74199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>0.33700000000000002</v>
+        <v>0.03</v>
       </c>
       <c r="D6">
-        <v>0.214</v>
+        <v>6.3E-2</v>
       </c>
       <c r="E6">
-        <v>0.253</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="F6">
-        <v>0.34</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="G6">
-        <v>0.41399999999999998</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="H6">
-        <v>0.51</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="I6">
-        <v>0.59099999999999997</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="J6">
-        <v>0.65100000000000002</v>
+        <v>0.61699999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="C7">
-        <v>0.29899999999999999</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="D7">
-        <v>0.41</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="E7">
-        <v>0.48699999999999999</v>
+        <v>0.48299999999999998</v>
       </c>
       <c r="F7">
-        <v>0.56299999999999994</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="G7">
-        <v>0.64100000000000001</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="H7">
         <v>0.71799999999999997</v>
       </c>
       <c r="I7">
-        <v>0.75800000000000001</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="J7">
-        <v>0.82099999999999995</v>
+        <v>0.82499999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="C8">
-        <v>4.3999999999999997E-2</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="D8">
-        <v>0.29599999999999999</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="E8">
-        <v>0.41899999999999998</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F8">
-        <v>0.52300000000000002</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="G8">
-        <v>0.61399999999999999</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="H8">
-        <v>0.68</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="I8">
-        <v>0.57299999999999995</v>
+        <v>0.83</v>
       </c>
       <c r="J8">
-        <v>0.59899999999999998</v>
+        <v>0.85499999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="C9">
-        <v>0.10100000000000001</v>
+        <v>2E-3</v>
       </c>
       <c r="D9">
-        <v>0.58499999999999996</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="E9">
-        <v>0.70499999999999996</v>
+        <v>0.127</v>
       </c>
       <c r="F9">
-        <v>0.45700000000000002</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="G9">
-        <v>0.45900000000000002</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="H9">
-        <v>0.499</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="I9">
-        <v>0.54</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="J9">
-        <v>0.56699999999999995</v>
+        <v>0.54500000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/pgroups4.xlsx
+++ b/xlsx/Power/pgroups4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161D9D25-D37D-4E97-A85E-B29A10E7F5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA19886-96AB-42F5-BCBB-E19472F8E80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1630A4E4-CC0E-43EA-BDFD-FFFD95EF5ED6}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1630A4E4-CC0E-43EA-BDFD-FFFD95EF5ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,22 +398,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.13800000000000001</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="B1">
-        <v>0.28499999999999998</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="C1">
-        <v>0.41599999999999998</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="D1">
-        <v>0.56499999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="E1">
-        <v>0.64700000000000002</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="F1">
-        <v>0.70499999999999996</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="G1">
         <v>0.78900000000000003</v>
@@ -422,18 +422,18 @@
         <v>0.82699999999999996</v>
       </c>
       <c r="I1">
-        <v>0.83799999999999997</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="J1">
-        <v>0.879</v>
+        <v>0.88200000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9.2999999999999999E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="B2">
-        <v>0.17100000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="C2">
         <v>0.29199999999999998</v>
@@ -442,118 +442,118 @@
         <v>0.43</v>
       </c>
       <c r="E2">
-        <v>0.505</v>
+        <v>0.502</v>
       </c>
       <c r="F2">
-        <v>0.60199999999999998</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="G2">
-        <v>0.68300000000000005</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="H2">
-        <v>0.73799999999999999</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="I2">
-        <v>0.77</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="J2">
-        <v>0.80800000000000005</v>
+        <v>0.81100000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.13400000000000001</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="B3">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
       <c r="C3">
-        <v>0.36299999999999999</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="D3">
-        <v>0.49299999999999999</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="E3">
-        <v>0.55800000000000005</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="F3">
-        <v>0.63400000000000001</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="H3">
-        <v>0.76800000000000002</v>
+        <v>0.77</v>
       </c>
       <c r="I3">
-        <v>0.77</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="J3">
-        <v>0.80300000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.12</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="B4">
-        <v>0.20899999999999999</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.30199999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="D4">
-        <v>0.41</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="E4">
-        <v>0.48599999999999999</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="F4">
-        <v>0.55800000000000005</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="G4">
-        <v>0.61799999999999999</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="H4">
-        <v>0.68899999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="I4">
-        <v>0.69399999999999995</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="J4">
-        <v>0.74199999999999999</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,33 +564,33 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>0.03</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D6">
-        <v>6.3E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="E6">
-        <v>0.14299999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="F6">
-        <v>0.28199999999999997</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="G6">
-        <v>0.38100000000000001</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="H6">
-        <v>0.48699999999999999</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="I6">
-        <v>0.56499999999999995</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="J6">
-        <v>0.61699999999999999</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.05</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="B7">
         <v>0.16600000000000001</v>
@@ -599,25 +599,25 @@
         <v>0.30199999999999999</v>
       </c>
       <c r="D7">
-        <v>0.41199999999999998</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="E7">
         <v>0.48299999999999998</v>
       </c>
       <c r="F7">
-        <v>0.57199999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="G7">
-        <v>0.65200000000000002</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="H7">
         <v>0.71799999999999997</v>
       </c>
       <c r="I7">
-        <v>0.76400000000000001</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="J7">
-        <v>0.82499999999999996</v>
+        <v>0.82399999999999995</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -631,13 +631,13 @@
         <v>0.50600000000000001</v>
       </c>
       <c r="D8">
-        <v>0.61899999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="E8">
-        <v>0.63900000000000001</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="F8">
-        <v>0.69099999999999995</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="G8">
         <v>0.73599999999999999</v>
@@ -646,7 +646,7 @@
         <v>0.78800000000000003</v>
       </c>
       <c r="I8">
-        <v>0.83</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="J8">
         <v>0.85499999999999998</v>
@@ -657,31 +657,31 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="B9">
-        <v>6.5000000000000002E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="C9">
         <v>2E-3</v>
       </c>
       <c r="D9">
-        <v>3.5999999999999997E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E9">
-        <v>0.127</v>
+        <v>0.122</v>
       </c>
       <c r="F9">
-        <v>0.30299999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="G9">
-        <v>0.38700000000000001</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="H9">
         <v>0.45800000000000002</v>
       </c>
       <c r="I9">
-        <v>0.50800000000000001</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="J9">
-        <v>0.54500000000000004</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
   </sheetData>
